--- a/UnityTableTool/Data/究极无敌雷霆爆炸长的表格名称.xlsx
+++ b/UnityTableTool/Data/究极无敌雷霆爆炸长的表格名称.xlsx
@@ -1560,7 +1560,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:14">
       <c r="A7" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2">
         <v>1007</v>
